--- a/output/roomself_excel/9959.xlsx
+++ b/output/roomself_excel/9959.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>443177</v>
+        <v>145935</v>
       </c>
       <c r="D2" t="n">
-        <v>8112</v>
+        <v>3164</v>
       </c>
       <c r="E2" t="n">
-        <v>1000</v>
+        <v>432</v>
       </c>
       <c r="F2" t="n">
-        <v>448</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>158943</v>
+        <v>244351</v>
       </c>
       <c r="D3" t="n">
-        <v>3520</v>
+        <v>4096</v>
       </c>
       <c r="E3" t="n">
-        <v>477</v>
+        <v>609</v>
       </c>
       <c r="F3" t="n">
-        <v>341</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48620</v>
+        <v>158943</v>
       </c>
       <c r="D4" t="n">
-        <v>1788</v>
+        <v>3520</v>
       </c>
       <c r="E4" t="n">
-        <v>177</v>
+        <v>477</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20880</v>
+        <v>91763</v>
       </c>
       <c r="D5" t="n">
-        <v>1156</v>
+        <v>2580</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>310</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24795</v>
+        <v>48620</v>
       </c>
       <c r="D6" t="n">
-        <v>1264</v>
+        <v>1788</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>91763</v>
+        <v>24854</v>
       </c>
       <c r="D7" t="n">
-        <v>2580</v>
+        <v>1488</v>
       </c>
       <c r="E7" t="n">
-        <v>312</v>
+        <v>151</v>
       </c>
       <c r="F7" t="n">
-        <v>310</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -598,19 +598,85 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24854</v>
+        <v>20880</v>
       </c>
       <c r="D8" t="n">
-        <v>1488</v>
+        <v>1156</v>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>297</v>
+      </c>
+      <c r="D9" t="n">
+        <v>897</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>52594</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2604</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24795</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E11" t="n">
+        <v>171</v>
+      </c>
+      <c r="F11" t="n">
         <v>16</v>
       </c>
     </row>

--- a/output/roomself_excel/9959.xlsx
+++ b/output/roomself_excel/9959.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3164</v>
       </c>
-      <c r="E2" t="n">
-        <v>432</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>391</v>
+        <v>375</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>416</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>4096</v>
       </c>
-      <c r="E3" t="n">
-        <v>609</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>431</v>
+        <v>415</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>593</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>3520</v>
       </c>
-      <c r="E4" t="n">
-        <v>477</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>341</v>
+        <v>461</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>325</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2580</v>
       </c>
-      <c r="E5" t="n">
-        <v>310</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>296</v>
+        <v>280</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>294</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +647,12 @@
       <c r="D6" t="n">
         <v>1788</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>1488</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>151</v>
       </c>
-      <c r="F7" t="n">
-        <v>16</v>
-      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1156</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>144</v>
       </c>
-      <c r="F8" t="n">
-        <v>16</v>
-      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,12 @@
       <c r="D9" t="n">
         <v>897</v>
       </c>
-      <c r="E9" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +751,12 @@
       <c r="D10" t="n">
         <v>2604</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +773,20 @@
       <c r="D11" t="n">
         <v>1264</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>171</v>
       </c>
-      <c r="F11" t="n">
-        <v>16</v>
-      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
